--- a/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1239_FinterestCoLtd.xlsx
+++ b/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1239_FinterestCoLtd.xlsx
@@ -382,17 +382,6 @@
     <t xml:space="preserve">SPX20-X</t>
   </si>
   <si>
-    <t xml:space="preserve">EVO25</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ライダー</t>
-    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -400,10 +389,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">2026.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -411,7 +406,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026.9</t>
+      <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
@@ -419,7 +414,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">に</t>
+      <t xml:space="preserve">か月分お支払い済み（みなし年払いは年</t>
     </r>
     <r>
       <rPr>
@@ -428,7 +423,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -436,7 +431,20 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">か月分お支払い済み（みなし年払いは年</t>
+      <t xml:space="preserve">回のため今回は対象外）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">EVO25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライダー</t>
     </r>
     <r>
       <rPr>
@@ -446,14 +454,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回のため今回は対象外）</t>
     </r>
   </si>
   <si>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1519,10 +1519,10 @@
         <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>1</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1645,10 +1645,10 @@
         <v>37</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1</v>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1771,7 +1771,7 @@
         <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>25</v>
@@ -1813,7 +1813,7 @@
         <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>25</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1855,7 +1855,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>25</v>
@@ -1939,7 +1939,7 @@
         <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>25</v>
@@ -1981,7 +1981,7 @@
         <v>54</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>25</v>
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2065,7 +2065,7 @@
         <v>58</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>25</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2149,7 +2149,7 @@
         <v>62</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>25</v>
@@ -2191,7 +2191,7 @@
         <v>64</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>25</v>
@@ -2233,7 +2233,7 @@
         <v>67</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>25</v>
@@ -2275,7 +2275,7 @@
         <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>25</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2485,7 +2485,7 @@
         <v>79</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>25</v>
@@ -2527,7 +2527,7 @@
         <v>81</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>25</v>
@@ -2569,7 +2569,7 @@
         <v>83</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>25</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2695,7 +2695,7 @@
         <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>25</v>
@@ -2737,7 +2737,7 @@
         <v>91</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>25</v>
@@ -2863,10 +2863,10 @@
         <v>95</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>1</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3031,7 +3031,7 @@
         <v>103</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>25</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3199,10 +3199,10 @@
         <v>60</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>1</v>
@@ -3241,10 +3241,10 @@
         <v>73</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>1</v>
@@ -3493,7 +3493,7 @@
         <v>121</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>25</v>
@@ -3535,7 +3535,7 @@
         <v>123</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>25</v>
